--- a/zeugnis-vorlage.xlsx
+++ b/zeugnis-vorlage.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -463,75 +463,73 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Seite</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
+          <t>Kommentar</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Kommentar</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr"/>
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Fach</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Kompetenz</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Subkompetenz</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Bewertung</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Fachkommentar</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Fach</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Kompetenz</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>Subkompetenz</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>Bewertung</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>Fachkommentar</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Deutsch</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Sprechen und Zuhören</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Du gibst Informationen korrekt wieder.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Deutsch</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Sprechen und Zuhören</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Du gibst Informationen korrekt wieder.</t>
+          <t>Du beziehst dich auf die Beiträge anderer.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
@@ -542,7 +540,7 @@
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Du beziehst dich auf die Beiträge anderer.</t>
+          <t>Du kannst grammatikalisch richtige Sätze bilden.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
@@ -550,10 +548,14 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Lesen und Texte rezipieren</t>
+        </is>
+      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Du kannst grammatikalisch richtige Sätze bilden.</t>
+          <t>Du kannst altersgemäße Texte in angemessener Zeit lesen und verstehen.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
@@ -561,14 +563,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Lesen und Texte rezipieren</t>
-        </is>
-      </c>
+      <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Du kannst altersgemäße Texte in angemessener Zeit lesen und verstehen.</t>
+          <t>Du kannst Fragen zum Gelesenen mündlich und schriftlich beantworten.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
@@ -579,7 +577,7 @@
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Fragen zum Gelesenen mündlich und schriftlich beantworten.</t>
+          <t>Du markierst wichtige Aussagen eines Textes passend.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
@@ -590,7 +588,7 @@
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Du markierst wichtige Aussagen eines Textes passend.</t>
+          <t>Du kannst den Inhalt des Gelesenen in Stichworten notieren.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
@@ -601,7 +599,7 @@
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Du kannst den Inhalt des Gelesenen in Stichworten notieren.</t>
+          <t>Du kannst wichtige Inhalte des Gelesenen erfassen und mithilfe von Textstellen belegen.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
@@ -612,7 +610,7 @@
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Du kannst wichtige Inhalte des Gelesenen erfassen und mithilfe von Textstellen belegen.</t>
+          <t>Du äußerst zu altersgemäßen Texten eigene Gedanken und Einschätzungen.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
@@ -623,7 +621,7 @@
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Du äußerst zu altersgemäßen Texten eigene Gedanken und Einschätzungen.</t>
+          <t>Du kannst geübte Texte flüssig und mit Betonung vorlesen.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
@@ -631,10 +629,14 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Schreiben</t>
+        </is>
+      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Du kannst geübte Texte flüssig und mit Betonung vorlesen.</t>
+          <t>Du schreibst lesbar und zügig.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -642,14 +644,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Schreiben</t>
-        </is>
-      </c>
+      <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Du schreibst lesbar und zügig.</t>
+          <t>Du wendest Rechtschreibstrategien auch bei unbekannten Wörtern richtig an.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
@@ -660,7 +658,7 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Du wendest Rechtschreibstrategien auch bei unbekannten Wörtern richtig an.</t>
+          <t>Du schreibst geübte Wörter aus dem Grundwortschatz richtig.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -671,7 +669,7 @@
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Du schreibst geübte Wörter aus dem Grundwortschatz richtig.</t>
+          <t>Du schreibst Nomen und Satzanfänge groß.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
@@ -682,7 +680,7 @@
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Du schreibst Nomen und Satzanfänge groß.</t>
+          <t>Du hältst Wort- und Satzgrenzen ein.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -693,7 +691,7 @@
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Du hältst Wort- und Satzgrenzen ein.</t>
+          <t>Du gliederst deine Texte übersichtlich.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
@@ -704,7 +702,7 @@
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Du gliederst deine Texte übersichtlich.</t>
+          <t>Du schreibst fehlerfrei ab.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -715,7 +713,7 @@
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Du schreibst fehlerfrei ab.</t>
+          <t>Du kannst das Wörterbuch als Rechtschreibhilfe nutzen.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -726,7 +724,7 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Du kannst das Wörterbuch als Rechtschreibhilfe nutzen.</t>
+          <t>Du kannst vollständige, grammatikalisch richtige Sätze schreiben.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -737,7 +735,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Du kannst vollständige, grammatikalisch richtige Sätze schreiben.</t>
+          <t>Du schreibst Geschichten, Berichte und Personenbeschreibungen nach besprochenen Kriterien.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -748,7 +746,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Du schreibst Geschichten, Berichte und Personenbeschreibungen nach besprochenen Kriterien.</t>
+          <t>Du entwickelst Schreibideen für Texte.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -759,7 +757,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Du entwickelst Schreibideen für Texte.</t>
+          <t>Du gestaltest eigene Texte mit Hilfe sprachlicher Mittel (z. B. wechselnde Satzanfänge, passende Zeitformen, wörtliche Rede).</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
@@ -770,7 +768,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Du gestaltest eigene Texte mit Hilfe sprachlicher Mittel (z. B. wechselnde Satzanfänge, passende Zeitformen, wörtliche Rede).</t>
+          <t>Du reflektierst und überarbeitest deine Texte.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -781,7 +779,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Du reflektierst und überarbeitest deine Texte.</t>
+          <t>Du präsentierst deine Texte vor anderen.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
@@ -789,10 +787,14 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr"/>
-      <c r="B30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Sprache untersuchen</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Du präsentierst deine Texte vor anderen.</t>
+          <t>Du ordnest Wörter den Wortarten Nomen, Adjektive, Verben, Artikel, Präpositionen und Pronomen passend zu.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
@@ -800,14 +802,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr"/>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Sprache untersuchen</t>
-        </is>
-      </c>
+      <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Du ordnest Wörter den Wortarten Nomen, Adjektive, Verben, Artikel, Präpositionen und Pronomen passend zu.</t>
+          <t>Du unterscheidest Aussage-, Frage- und Ausrufesatz und verwendest die passenden Satzschlusszeichen.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
@@ -818,7 +816,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Du unterscheidest Aussage-, Frage- und Ausrufesatz und verwendest die passenden Satzschlusszeichen.</t>
+          <t>Du erkennst die wörtliche Rede und setzt die passenden Satzzeichen.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -829,7 +827,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Du erkennst die wörtliche Rede und setzt die passenden Satzzeichen.</t>
+          <t>Du benennst und bildest Verbformen in verschiedenen Zeiten (Präsens, Präteritum, Perfekt) richtig.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
@@ -840,37 +838,37 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Du benennst und bildest Verbformen in verschiedenen Zeiten (Präsens, Präteritum, Perfekt) richtig.</t>
+          <t>Du kannst Wörter nach dem Alphabet sortieren und nachschlagen.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="2" t="inlineStr"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Mathematik</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Zahl und Operation (Zahlenraum bis 1.000)</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Wörter nach dem Alphabet sortieren und nachschlagen.</t>
+          <t>Du kannst dich im Zahlenraum bis 1000 orientieren.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Mathematik</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Zahl und Operation (Zahlenraum bis 1.000)</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Du kannst dich im Zahlenraum bis 1000 orientieren.</t>
+          <t>Du kannst Additionsaufgaben (+) mit und ohne Übergänge lösen.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
@@ -881,7 +879,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Additionsaufgaben (+) mit und ohne Übergänge lösen.</t>
+          <t>Du kannst Additionsaufgaben halbschriftlich und schriftlich lösen.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
@@ -892,7 +890,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Additionsaufgaben halbschriftlich und schriftlich lösen.</t>
+          <t>Du kannst Subtraktionsaufgaben (-) mit und ohne Übergänge lösen.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
@@ -903,7 +901,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Subtraktionsaufgaben (-) mit und ohne Übergänge lösen.</t>
+          <t>Du kannst Subtraktionsaufgaben mit Übertrag halbschriftlich und schriftlich lösen.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
@@ -914,7 +912,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Subtraktionsaufgaben mit Übertrag halbschriftlich und schriftlich lösen.</t>
+          <t>Du löst die Multiplikationsaufgaben (*) des kleinen Einmaleins automatisiert.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
@@ -925,7 +923,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Du löst die Multiplikationsaufgaben (*) des kleinen Einmaleins automatisiert.</t>
+          <t>Du löst die Divisionsaufgaben (:) des kleinen Einmaleins automatisiert.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
@@ -936,7 +934,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Du löst die Divisionsaufgaben (:) des kleinen Einmaleins automatisiert.</t>
+          <t>Du kannst Divisionsaufgaben (:) mit Rest lösen.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -947,7 +945,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Divisionsaufgaben (:) mit Rest lösen.</t>
+          <t>Du wählst geeignete Rechenstrategien aus und wendest sie an.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -958,7 +956,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Du wählst geeignete Rechenstrategien aus und wendest sie an.</t>
+          <t>Du nutzt geeignete Verfahren, um deine Ergebnisse zu überprüfen.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -969,7 +967,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Du nutzt geeignete Verfahren, um deine Ergebnisse zu überprüfen.</t>
+          <t>Du kannst Sachaufgaben verstehen und eine passende Fragestellung entwickeln.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -980,7 +978,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Sachaufgaben verstehen und eine passende Fragestellung entwickeln.</t>
+          <t>Du kannst zu Sachaufgaben Lösungswege finden und eine passende Antwort formulieren.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -988,10 +986,14 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr"/>
-      <c r="B47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Raum und Form</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Du kannst zu Sachaufgaben Lösungswege finden und eine passende Antwort formulieren.</t>
+          <t>Du kannst geometrischen Grundformen benennen und ihre besonderen Merkmale mit Fachbegriffen beschreiben.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -999,14 +1001,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr"/>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Raum und Form</t>
-        </is>
-      </c>
+      <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Du kannst geometrischen Grundformen benennen und ihre besonderen Merkmale mit Fachbegriffen beschreiben.</t>
+          <t>Du kannst geometrische Formen mit und ohne Lineal zeichnen.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -1017,7 +1015,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Du kannst geometrische Formen mit und ohne Lineal zeichnen.</t>
+          <t>Du vergrößerst oder verkleinerst Figuren nach Vorgaben.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -1028,7 +1026,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Du vergrößerst oder verkleinerst Figuren nach Vorgaben.</t>
+          <t>Du erkennst komplexere geometrische Muster und kannst diese fortsetzen.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -1039,7 +1037,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Du erkennst komplexere geometrische Muster und kannst diese fortsetzen.</t>
+          <t>Du kannst geometrische Körper benennen, mit Fachbegriffen beschreiben sie vergleichen und ihnen die entsprechenden Körpernetze zuordnen.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -1050,7 +1048,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Du kannst geometrische Körper benennen, mit Fachbegriffen beschreiben sie vergleichen und ihnen die entsprechenden Körpernetze zuordnen.</t>
+          <t>Du überprüfst Figuren auf Achsensymmetrie und kannst zur Spiegelachse symmetrisch ergänzen.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -1061,7 +1059,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Du überprüfst Figuren auf Achsensymmetrie und kannst zur Spiegelachse symmetrisch ergänzen.</t>
+          <t>Du kannst Lagebeziehungen und Ansichten beschreiben.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -1072,7 +1070,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Lagebeziehungen und Ansichten beschreiben.</t>
+          <t>Du kannst Lagepläne lesen und zeichnen sowie Wege auf Lageplänen finden, beschreiben und zeichnen.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -1080,10 +1078,14 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Größen und Messen</t>
+        </is>
+      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Lagepläne lesen und zeichnen sowie Wege auf Lageplänen finden, beschreiben und zeichnen.</t>
+          <t>Du kannst Uhrzeiten sekundengenau ablesen, einstellen und notieren.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -1091,14 +1093,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr"/>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Größen und Messen</t>
-        </is>
-      </c>
+      <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Uhrzeiten sekundengenau ablesen, einstellen und notieren.</t>
+          <t>Du kannst Zeitspannen bestimmen.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -1109,7 +1107,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Zeitspannen bestimmen.</t>
+          <t>Du kannst Repräsentanten zu den Längeneinheiten mm, cm, m und km benennen und Längen abmessen.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -1120,7 +1118,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Repräsentanten zu den Längeneinheiten mm, cm, m und km benennen und Längen abmessen.</t>
+          <t>Du kannst Längenangaben in unterschiedlichen Schreibweisen darstellen.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -1131,7 +1129,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Längenangaben in unterschiedlichen Schreibweisen darstellen.</t>
+          <t>Du kannst Repräsentanten zu den Gewichtseinheiten g, kg und t benennen und Objekte wiegen.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -1142,7 +1140,7 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Repräsentanten zu den Gewichtseinheiten g, kg und t benennen und Objekte wiegen.</t>
+          <t>Du kannst Gewichtsangaben in unterschiedlichen Schreibweisen darstellen.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -1153,7 +1151,7 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Gewichtsangaben in unterschiedlichen Schreibweisen darstellen.</t>
+          <t>Du kannst Geldbeträge mit Scheinen und Münzen darstellen, miteinander vergleichen und ordnen.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -1164,7 +1162,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Geldbeträge mit Scheinen und Münzen darstellen, miteinander vergleichen und ordnen.</t>
+          <t>Du kannst mit Geldbeträgen rechnen.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -1172,10 +1170,14 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr"/>
-      <c r="B63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Daten und Zufall</t>
+        </is>
+      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Du kannst mit Geldbeträgen rechnen.</t>
+          <t>Du kannst Daten aus einer Tabelle oder einem Diagramm ablesen bzw. selbst erheben und in eine andere Darstellungsform übertragen.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
@@ -1183,14 +1185,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr"/>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Daten und Zufall</t>
-        </is>
-      </c>
+      <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Daten aus einer Tabelle oder einem Diagramm ablesen bzw. selbst erheben und in eine andere Darstellungsform übertragen.</t>
+          <t>Du kannst kombinatorische Aufgaben durch systematisches Vorgehen lösen und deine Lösung strategisch darstellen.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -1201,7 +1199,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Du kannst kombinatorische Aufgaben durch systematisches Vorgehen lösen und deine Lösung strategisch darstellen.</t>
+          <t>Du kannst Wahrscheinlichkeiten von einfachen Zufallsversuchen einschätzen, die Ergebnisse beschreiben und miteinander vergleichen.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -1209,10 +1207,14 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr"/>
-      <c r="B66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Problemlösen, Modellieren, Argumentieren, Darstellen/Kommunizieren</t>
+        </is>
+      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Wahrscheinlichkeiten von einfachen Zufallsversuchen einschätzen, die Ergebnisse beschreiben und miteinander vergleichen.</t>
+          <t>Du stellst deine Ideen verständlich dar und kannst deinen Lösungsweg erklären sowie mit anderen vergleichen.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -1220,44 +1222,40 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Problemlösen, Modellieren, Argumentieren, Darstellen/Kommunizieren</t>
-        </is>
-      </c>
+      <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Du stellst deine Ideen verständlich dar und kannst deinen Lösungsweg erklären sowie mit anderen vergleichen.</t>
+          <t>Du kannst Begründungen und Argumente formulieren.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr"/>
-      <c r="B68" s="2" t="inlineStr"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Sachunterricht</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Erkenntnisgewinnung</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Begründungen und Argumente formulieren.</t>
+          <t>Du kannst zielführend Fragen stellen, um Wissen zu erwerben und Sachthemen zu verstehen.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Sachunterricht</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Erkenntnisgewinnung</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Du kannst zielführend Fragen stellen, um Wissen zu erwerben und Sachthemen zu verstehen.</t>
+          <t>Du kannst zu Sachthemen recherchieren, indem du verschiedene Quellen (Sachtexte, Interviews, Bild-, Text- und Sachquellen) auswertest.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -1268,7 +1266,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Du kannst zu Sachthemen recherchieren, indem du verschiedene Quellen (Sachtexte, Interviews, Bild-, Text- und Sachquellen) auswertest.</t>
+          <t>Du kannst einen Versuch (zum Pflanzenwachstum, zum Sprudelgas, zur magnetischen Wirkung von Strom) planen, aufbauen, durchführen und auswerten.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -1279,7 +1277,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Du kannst einen Versuch (zum Pflanzenwachstum, zum Sprudelgas, zur magnetischen Wirkung von Strom) planen, aufbauen, durchführen und auswerten.</t>
+          <t>Du kannst Daten zu (untersuchten Bereich einfügen) erheben, darstellen und auswerten.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
@@ -1290,7 +1288,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Daten zu (untersuchten Bereich einfügen) erheben, darstellen und auswerten.</t>
+          <t>Du kannst (Stadtpläne, Baupläne, mehrschrittige Anleitungen, PC-Programme, Apps) lesen und nutzen.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -1301,7 +1299,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Du kannst (Stadtpläne, Baupläne, mehrschrittige Anleitungen, PC-Programme, Apps) lesen und nutzen.</t>
+          <t>Du wendest Problemlösestrategien (im Klassenrat, bei Interessenskonflikten, bei technischen Fragestellungen) an.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -1312,7 +1310,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Du wendest Problemlösestrategien (im Klassenrat, bei Interessenskonflikten, bei technischen Fragestellungen) an.</t>
+          <t>Du kannst (Modelle, technische Konstruktionen) (planen, bauen, erklären) und dadurch Erkenntnisse über (Fahrzeuge, Türme, Brücken, Pflanzen, Körperteile) gewinnen.</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -1320,10 +1318,14 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr"/>
-      <c r="B75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Kommunikation</t>
+        </is>
+      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Du kannst (Modelle, technische Konstruktionen) (planen, bauen, erklären) und dadurch Erkenntnisse über (Fahrzeuge, Türme, Brücken, Pflanzen, Körperteile) gewinnen.</t>
+          <t>Du bringst dich in Unterrichtsgesprächen aktiv ein und zeigst dadurch dein Interesse an Sachthemen.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -1331,14 +1333,10 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr"/>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Kommunikation</t>
-        </is>
-      </c>
+      <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Du bringst dich in Unterrichtsgesprächen aktiv ein und zeigst dadurch dein Interesse an Sachthemen.</t>
+          <t>Du kannst Beobachtungen und Vermutungen von/ zu (Pflanzen, Tieren, Bildern, Gegenständen) äußern.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -1349,7 +1347,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Beobachtungen und Vermutungen von/ zu (Pflanzen, Tieren, Bildern, Gegenständen) äußern.</t>
+          <t>Du verwendest treffende Begriffe und sachlich angemessene Darstellungen (Symbole, Zeichnungen) zu den Sachthemen (Unterrichtsthemen einfügen).</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -1360,7 +1358,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Du verwendest treffende Begriffe und sachlich angemessene Darstellungen (Symbole, Zeichnungen) zu den Sachthemen (Unterrichtsthemen einfügen).</t>
+          <t>Du nutzt geeignete Präsentations- und Darstellungsformen nach besprochenen Kriterien.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -1368,10 +1366,14 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr"/>
-      <c r="B79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Bewertung</t>
+        </is>
+      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Du nutzt geeignete Präsentations- und Darstellungsformen nach besprochenen Kriterien.</t>
+          <t>Du kannst mit anderen darüber diskutieren, ob Dargestelltes real oder fiktiv ist.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -1379,14 +1381,10 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr"/>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Bewertung</t>
-        </is>
-      </c>
+      <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Du kannst mit anderen darüber diskutieren, ob Dargestelltes real oder fiktiv ist.</t>
+          <t>Du kannst (Ereignisse, Gegenstände) in der Zeit einordnen.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
@@ -1397,7 +1395,7 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Du kannst (Ereignisse, Gegenstände) in der Zeit einordnen.</t>
+          <t>Du benennst Maßnahmen zur Erhaltung der eigenen Gesundheit (Zähne/ gesunde Ernährung/ mein Körper).</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -1408,7 +1406,7 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Du benennst Maßnahmen zur Erhaltung der eigenen Gesundheit (Zähne/ gesunde Ernährung/ mein Körper).</t>
+          <t>Du kannst beschreiben, dass Umwelt und Natur im Sinne der Nachhaltigkeit geschützt werden müssen und gehst respektvoll mit Lebewesen um.</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -1419,18 +1417,22 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Du kannst beschreiben, dass Umwelt und Natur im Sinne der Nachhaltigkeit geschützt werden müssen und gehst respektvoll mit Lebewesen um.</t>
+          <t>Du kennst die Grundsätze des demokratischen Systems und wendest sie (im Klassenrat, bei Entscheidungsfindungen, politischen Diskussionen) an.</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Du kennst die Grundsätze des demokratischen Systems und wendest sie (im Klassenrat, bei Entscheidungsfindungen, politischen Diskussionen) an.</t>
+          <t>(Kompetenzen hier ergänzen)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
@@ -1439,7 +1441,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Englisch</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr"/>
@@ -1454,7 +1456,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr"/>
@@ -1469,28 +1471,24 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Religion</t>
+          <t>Kunst</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>(Kompetenzen hier ergänzen)</t>
+          <t>Du beteiligst dich an Unterrichtsgesprächen und zeigst so Interesse an künstlerischen Themen.</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Kunst</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="inlineStr"/>
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Du beteiligst dich an Unterrichtsgesprächen und zeigst so Interesse an künstlerischen Themen.</t>
+          <t>Du nutzt Buntstifte, Wasserfarben, Acrylfarben und selbst ausgewählte Bastelmaterialien für deine Werke.</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
@@ -1501,7 +1499,7 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Du nutzt Buntstifte, Wasserfarben, Acrylfarben und selbst ausgewählte Bastelmaterialien für deine Werke.</t>
+          <t>Du beachtest gestalterische Kriterien bei der Umsetzung eines Themas.</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
@@ -1512,7 +1510,7 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Du beachtest gestalterische Kriterien bei der Umsetzung eines Themas.</t>
+          <t>Du hast eigene Ideen zur Gestaltung.</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -1523,7 +1521,7 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Du hast eigene Ideen zur Gestaltung.</t>
+          <t>Du setzt deine Ideen selbstständig um.</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -1534,7 +1532,7 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Du setzt deine Ideen selbstständig um.</t>
+          <t>Du stellst deine Werke in der vorgesehenen Zeit sinnvoll fertig.</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -1545,7 +1543,7 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Du stellst deine Werke in der vorgesehenen Zeit sinnvoll fertig.</t>
+          <t>Du kannst Tipps annehmen und sinnvoll für die eigene Arbeit nutzen.</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
@@ -1556,7 +1554,7 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Tipps annehmen und sinnvoll für die eigene Arbeit nutzen.</t>
+          <t>Du kannst deine eigenen Kunstwerke und die anderer Künstler beschreiben.</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
@@ -1567,7 +1565,7 @@
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Du kannst deine eigenen Kunstwerke und die anderer Künstler beschreiben.</t>
+          <t>Du begründest deine Meinung zu Kunstwerken.</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
@@ -1578,7 +1576,7 @@
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Du begründest deine Meinung zu Kunstwerken.</t>
+          <t>Du kennst Fachbegriffe und nutzt sie passend.</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
@@ -1589,33 +1587,33 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Du kennst Fachbegriffe und nutzt sie passend.</t>
+          <t>Du kannst ausdrücken, ob du dich an die Gestaltungsvorgaben gehalten hast.</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr"/>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Musik</t>
+        </is>
+      </c>
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Du kannst ausdrücken, ob du dich an die Gestaltungsvorgaben gehalten hast.</t>
+          <t>Du beteiligst dich interessiert an den musikalischen Aktivitäten.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>Musik</t>
-        </is>
-      </c>
+      <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Du beteiligst dich interessiert an den musikalischen Aktivitäten.</t>
+          <t>Du beteiligst dich aktiv an Unterrichtsgesprächen.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
@@ -1626,7 +1624,7 @@
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Du beteiligst dich aktiv an Unterrichtsgesprächen.</t>
+          <t>Du findest passende Bewegungen und entwickelst Choreografien zu unterschiedlicher Musik.</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
@@ -1637,7 +1635,7 @@
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Du findest passende Bewegungen und entwickelst Choreografien zu unterschiedlicher Musik.</t>
+          <t>Du kannst Rhythmen umsetzen.</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
@@ -1648,7 +1646,7 @@
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Rhythmen umsetzen.</t>
+          <t>Du singst unsere Lieder mit.</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
@@ -1659,7 +1657,7 @@
       <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Du singst unsere Lieder mit.</t>
+          <t>Du tanzt vorgegebene Tänze nach.</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr"/>
@@ -1670,7 +1668,7 @@
       <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Du tanzt vorgegebene Tänze nach.</t>
+          <t>Du kennst alle Orff-Instrumente und spielst sie rhythmisch und technisch korrekt.</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
@@ -1681,7 +1679,7 @@
       <c r="B105" s="2" t="inlineStr"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Du kennst alle Orff-Instrumente und spielst sie rhythmisch und technisch korrekt.</t>
+          <t>Du kennst Orchester-Instrumente.</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
@@ -1692,7 +1690,7 @@
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Du kennst Orchester-Instrumente.</t>
+          <t>Du kennst musikalische Gestaltungsmittel wie hoch-tief, laut-leise, schnell-langsam, traurig-fröhlich und kannst sie umsetzen.</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
@@ -1703,7 +1701,7 @@
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Du kennst musikalische Gestaltungsmittel wie hoch-tief, laut-leise, schnell-langsam, traurig-fröhlich und kannst sie umsetzen.</t>
+          <t>Du kannst Notenwerte benennen und umsetzen.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
@@ -1714,22 +1712,11 @@
       <c r="B108" s="2" t="inlineStr"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Notenwerte benennen und umsetzen.</t>
+          <t>Du nutzt musikalische Fachbegriffe.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr"/>
-      <c r="B109" s="2" t="inlineStr"/>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Du nutzt musikalische Fachbegriffe.</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr"/>
-      <c r="E109" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/zeugnis-vorlage.xlsx
+++ b/zeugnis-vorlage.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -441,9 +441,17 @@
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
+      <c r="C1" s="2" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Bewertung</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bedeutung</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -456,9 +464,17 @@
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>sicher</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -467,106 +483,126 @@
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>überwiegend</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>teilweise</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Fach</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Kompetenz</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>Subkompetenz</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>Bewertung</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>Fachkommentar</t>
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>mit Unterstützung</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Deutsch</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Sprechen und Zuhören</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Du gibst Informationen korrekt wieder.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>noch nicht erworben (→)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Du beziehst dich auf die Beiträge anderer.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>siehe Kommentar</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Du kannst grammatikalisch richtige Sätze bilden.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Lesen und Texte rezipieren</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Du kannst altersgemäße Texte in angemessener Zeit lesen und verstehen.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Fach</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Kompetenz</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Fähigkeit</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>Bewertung</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Fachkommentar</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Deutsch</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sprechen und Zuhören</t>
+        </is>
+      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Fragen zum Gelesenen mündlich und schriftlich beantworten.</t>
+          <t>Du gibst Informationen korrekt wieder.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
@@ -577,7 +613,7 @@
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Du markierst wichtige Aussagen eines Textes passend.</t>
+          <t>Du beziehst dich auf die Beiträge anderer.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
@@ -588,7 +624,7 @@
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Du kannst den Inhalt des Gelesenen in Stichworten notieren.</t>
+          <t>Du kannst grammatikalisch richtige Sätze bilden.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
@@ -596,10 +632,14 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Lesen und Texte rezipieren</t>
+        </is>
+      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Du kannst wichtige Inhalte des Gelesenen erfassen und mithilfe von Textstellen belegen.</t>
+          <t>Du kannst altersgemäße Texte in angemessener Zeit lesen und verstehen.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
@@ -610,7 +650,7 @@
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Du äußerst zu altersgemäßen Texten eigene Gedanken und Einschätzungen.</t>
+          <t>Du kannst Fragen zum Gelesenen mündlich und schriftlich beantworten.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
@@ -621,7 +661,7 @@
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Du kannst geübte Texte flüssig und mit Betonung vorlesen.</t>
+          <t>Du markierst wichtige Aussagen eines Textes passend.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
@@ -629,14 +669,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Schreiben</t>
-        </is>
-      </c>
+      <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Du schreibst lesbar und zügig.</t>
+          <t>Du kannst den Inhalt des Gelesenen in Stichworten notieren.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -647,7 +683,7 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Du wendest Rechtschreibstrategien auch bei unbekannten Wörtern richtig an.</t>
+          <t>Du kannst wichtige Inhalte des Gelesenen erfassen und mithilfe von Textstellen belegen.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
@@ -658,7 +694,7 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Du schreibst geübte Wörter aus dem Grundwortschatz richtig.</t>
+          <t>Du äußerst zu altersgemäßen Texten eigene Gedanken und Einschätzungen.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -669,7 +705,7 @@
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Du schreibst Nomen und Satzanfänge groß.</t>
+          <t>Du kannst geübte Texte flüssig und mit Betonung vorlesen.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
@@ -677,10 +713,14 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr"/>
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Schreiben</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Du hältst Wort- und Satzgrenzen ein.</t>
+          <t>Du schreibst lesbar und zügig.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -691,7 +731,7 @@
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Du gliederst deine Texte übersichtlich.</t>
+          <t>Du wendest Rechtschreibstrategien auch bei unbekannten Wörtern richtig an.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
@@ -702,7 +742,7 @@
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Du schreibst fehlerfrei ab.</t>
+          <t>Du schreibst geübte Wörter aus dem Grundwortschatz richtig.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -713,7 +753,7 @@
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Du kannst das Wörterbuch als Rechtschreibhilfe nutzen.</t>
+          <t>Du schreibst Nomen und Satzanfänge groß.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -724,7 +764,7 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Du kannst vollständige, grammatikalisch richtige Sätze schreiben.</t>
+          <t>Du hältst Wort- und Satzgrenzen ein.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -735,7 +775,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Du schreibst Geschichten, Berichte und Personenbeschreibungen nach besprochenen Kriterien.</t>
+          <t>Du gliederst deine Texte übersichtlich.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -746,7 +786,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Du entwickelst Schreibideen für Texte.</t>
+          <t>Du schreibst fehlerfrei ab.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -757,7 +797,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Du gestaltest eigene Texte mit Hilfe sprachlicher Mittel (z. B. wechselnde Satzanfänge, passende Zeitformen, wörtliche Rede).</t>
+          <t>Du kannst das Wörterbuch als Rechtschreibhilfe nutzen.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
@@ -768,7 +808,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Du reflektierst und überarbeitest deine Texte.</t>
+          <t>Du kannst vollständige, grammatikalisch richtige Sätze schreiben.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -779,7 +819,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Du präsentierst deine Texte vor anderen.</t>
+          <t>Du schreibst Geschichten, Berichte und Personenbeschreibungen nach besprochenen Kriterien.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
@@ -787,14 +827,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr"/>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Sprache untersuchen</t>
-        </is>
-      </c>
+      <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Du ordnest Wörter den Wortarten Nomen, Adjektive, Verben, Artikel, Präpositionen und Pronomen passend zu.</t>
+          <t>Du entwickelst Schreibideen für Texte.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
@@ -805,7 +841,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Du unterscheidest Aussage-, Frage- und Ausrufesatz und verwendest die passenden Satzschlusszeichen.</t>
+          <t>Du gestaltest eigene Texte mit Hilfe sprachlicher Mittel (z. B. wechselnde Satzanfänge, passende Zeitformen, wörtliche Rede).</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
@@ -816,7 +852,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Du erkennst die wörtliche Rede und setzt die passenden Satzzeichen.</t>
+          <t>Du reflektierst und überarbeitest deine Texte.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -827,7 +863,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Du benennst und bildest Verbformen in verschiedenen Zeiten (Präsens, Präteritum, Perfekt) richtig.</t>
+          <t>Du präsentierst deine Texte vor anderen.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
@@ -835,29 +871,25 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr"/>
-      <c r="B34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Sprache untersuchen</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Wörter nach dem Alphabet sortieren und nachschlagen.</t>
+          <t>Du ordnest Wörter den Wortarten Nomen, Adjektive, Verben, Artikel, Präpositionen und Pronomen passend zu.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Mathematik</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Zahl und Operation (Zahlenraum bis 1.000)</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Du kannst dich im Zahlenraum bis 1000 orientieren.</t>
+          <t>Du unterscheidest Aussage-, Frage- und Ausrufesatz und verwendest die passenden Satzschlusszeichen.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
@@ -868,7 +900,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Additionsaufgaben (+) mit und ohne Übergänge lösen.</t>
+          <t>Du erkennst die wörtliche Rede und setzt die passenden Satzzeichen.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
@@ -879,7 +911,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Additionsaufgaben halbschriftlich und schriftlich lösen.</t>
+          <t>Du benennst und bildest Verbformen in verschiedenen Zeiten (Präsens, Präteritum, Perfekt) richtig.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
@@ -890,18 +922,26 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Subtraktionsaufgaben (-) mit und ohne Übergänge lösen.</t>
+          <t>Du kannst Wörter nach dem Alphabet sortieren und nachschlagen.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="2" t="inlineStr"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Mathematik</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Zahl und Operation (Zahlenraum bis 1.000)</t>
+        </is>
+      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Subtraktionsaufgaben mit Übertrag halbschriftlich und schriftlich lösen.</t>
+          <t>Du kannst dich im Zahlenraum bis 1000 orientieren.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
@@ -912,7 +952,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Du löst die Multiplikationsaufgaben (*) des kleinen Einmaleins automatisiert.</t>
+          <t>Du kannst Additionsaufgaben (+) mit und ohne Übergänge lösen.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
@@ -923,7 +963,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Du löst die Divisionsaufgaben (:) des kleinen Einmaleins automatisiert.</t>
+          <t>Du kannst Additionsaufgaben halbschriftlich und schriftlich lösen.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
@@ -934,7 +974,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Divisionsaufgaben (:) mit Rest lösen.</t>
+          <t>Du kannst Subtraktionsaufgaben (-) mit und ohne Übergänge lösen.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -945,7 +985,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Du wählst geeignete Rechenstrategien aus und wendest sie an.</t>
+          <t>Du kannst Subtraktionsaufgaben mit Übertrag halbschriftlich und schriftlich lösen.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -956,7 +996,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Du nutzt geeignete Verfahren, um deine Ergebnisse zu überprüfen.</t>
+          <t>Du löst die Multiplikationsaufgaben (*) des kleinen Einmaleins automatisiert.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -967,7 +1007,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Sachaufgaben verstehen und eine passende Fragestellung entwickeln.</t>
+          <t>Du löst die Divisionsaufgaben (:) des kleinen Einmaleins automatisiert.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -978,7 +1018,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Du kannst zu Sachaufgaben Lösungswege finden und eine passende Antwort formulieren.</t>
+          <t>Du kannst Divisionsaufgaben (:) mit Rest lösen.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -986,14 +1026,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr"/>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Raum und Form</t>
-        </is>
-      </c>
+      <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Du kannst geometrischen Grundformen benennen und ihre besonderen Merkmale mit Fachbegriffen beschreiben.</t>
+          <t>Du wählst geeignete Rechenstrategien aus und wendest sie an.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -1004,7 +1040,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Du kannst geometrische Formen mit und ohne Lineal zeichnen.</t>
+          <t>Du nutzt geeignete Verfahren, um deine Ergebnisse zu überprüfen.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -1015,7 +1051,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Du vergrößerst oder verkleinerst Figuren nach Vorgaben.</t>
+          <t>Du kannst Sachaufgaben verstehen und eine passende Fragestellung entwickeln.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -1026,7 +1062,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Du erkennst komplexere geometrische Muster und kannst diese fortsetzen.</t>
+          <t>Du kannst zu Sachaufgaben Lösungswege finden und eine passende Antwort formulieren.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -1034,10 +1070,14 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr"/>
-      <c r="B51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Raum und Form</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Du kannst geometrische Körper benennen, mit Fachbegriffen beschreiben sie vergleichen und ihnen die entsprechenden Körpernetze zuordnen.</t>
+          <t>Du kannst geometrischen Grundformen benennen und ihre besonderen Merkmale mit Fachbegriffen beschreiben.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -1048,7 +1088,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Du überprüfst Figuren auf Achsensymmetrie und kannst zur Spiegelachse symmetrisch ergänzen.</t>
+          <t>Du kannst geometrische Formen mit und ohne Lineal zeichnen.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -1059,7 +1099,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Lagebeziehungen und Ansichten beschreiben.</t>
+          <t>Du vergrößerst oder verkleinerst Figuren nach Vorgaben.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -1070,7 +1110,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Lagepläne lesen und zeichnen sowie Wege auf Lageplänen finden, beschreiben und zeichnen.</t>
+          <t>Du erkennst komplexere geometrische Muster und kannst diese fortsetzen.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -1078,14 +1118,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Größen und Messen</t>
-        </is>
-      </c>
+      <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Uhrzeiten sekundengenau ablesen, einstellen und notieren.</t>
+          <t>Du kannst geometrische Körper benennen, mit Fachbegriffen beschreiben sie vergleichen und ihnen die entsprechenden Körpernetze zuordnen.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -1096,7 +1132,7 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Zeitspannen bestimmen.</t>
+          <t>Du überprüfst Figuren auf Achsensymmetrie und kannst zur Spiegelachse symmetrisch ergänzen.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -1107,7 +1143,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Repräsentanten zu den Längeneinheiten mm, cm, m und km benennen und Längen abmessen.</t>
+          <t>Du kannst Lagebeziehungen und Ansichten beschreiben.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -1118,7 +1154,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Längenangaben in unterschiedlichen Schreibweisen darstellen.</t>
+          <t>Du kannst Lagepläne lesen und zeichnen sowie Wege auf Lageplänen finden, beschreiben und zeichnen.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -1126,10 +1162,14 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr"/>
-      <c r="B59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Größen und Messen</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Repräsentanten zu den Gewichtseinheiten g, kg und t benennen und Objekte wiegen.</t>
+          <t>Du kannst Uhrzeiten sekundengenau ablesen, einstellen und notieren.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -1140,7 +1180,7 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Gewichtsangaben in unterschiedlichen Schreibweisen darstellen.</t>
+          <t>Du kannst Zeitspannen bestimmen.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -1151,7 +1191,7 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Geldbeträge mit Scheinen und Münzen darstellen, miteinander vergleichen und ordnen.</t>
+          <t>Du kannst Repräsentanten zu den Längeneinheiten mm, cm, m und km benennen und Längen abmessen.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -1162,7 +1202,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Du kannst mit Geldbeträgen rechnen.</t>
+          <t>Du kannst Längenangaben in unterschiedlichen Schreibweisen darstellen.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -1170,14 +1210,10 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr"/>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Daten und Zufall</t>
-        </is>
-      </c>
+      <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Daten aus einer Tabelle oder einem Diagramm ablesen bzw. selbst erheben und in eine andere Darstellungsform übertragen.</t>
+          <t>Du kannst Repräsentanten zu den Gewichtseinheiten g, kg und t benennen und Objekte wiegen.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
@@ -1188,7 +1224,7 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Du kannst kombinatorische Aufgaben durch systematisches Vorgehen lösen und deine Lösung strategisch darstellen.</t>
+          <t>Du kannst Gewichtsangaben in unterschiedlichen Schreibweisen darstellen.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -1199,7 +1235,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Wahrscheinlichkeiten von einfachen Zufallsversuchen einschätzen, die Ergebnisse beschreiben und miteinander vergleichen.</t>
+          <t>Du kannst Geldbeträge mit Scheinen und Münzen darstellen, miteinander vergleichen und ordnen.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -1207,14 +1243,10 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr"/>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Problemlösen, Modellieren, Argumentieren, Darstellen/Kommunizieren</t>
-        </is>
-      </c>
+      <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Du stellst deine Ideen verständlich dar und kannst deinen Lösungsweg erklären sowie mit anderen vergleichen.</t>
+          <t>Du kannst mit Geldbeträgen rechnen.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -1222,29 +1254,25 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Daten und Zufall</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Begründungen und Argumente formulieren.</t>
+          <t>Du kannst Daten aus einer Tabelle oder einem Diagramm ablesen bzw. selbst erheben und in eine andere Darstellungsform übertragen.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Sachunterricht</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Erkenntnisgewinnung</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Du kannst zielführend Fragen stellen, um Wissen zu erwerben und Sachthemen zu verstehen.</t>
+          <t>Du kannst kombinatorische Aufgaben durch systematisches Vorgehen lösen und deine Lösung strategisch darstellen.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -1255,7 +1283,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Du kannst zu Sachthemen recherchieren, indem du verschiedene Quellen (Sachtexte, Interviews, Bild-, Text- und Sachquellen) auswertest.</t>
+          <t>Du kannst Wahrscheinlichkeiten von einfachen Zufallsversuchen einschätzen, die Ergebnisse beschreiben und miteinander vergleichen.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -1263,10 +1291,14 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr"/>
-      <c r="B70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Problemlösen, Modellieren, Argumentieren, Darstellen/Kommunizieren</t>
+        </is>
+      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Du kannst einen Versuch (zum Pflanzenwachstum, zum Sprudelgas, zur magnetischen Wirkung von Strom) planen, aufbauen, durchführen und auswerten.</t>
+          <t>Du stellst deine Ideen verständlich dar und kannst deinen Lösungsweg erklären sowie mit anderen vergleichen.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -1277,18 +1309,26 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Daten zu (untersuchten Bereich einfügen) erheben, darstellen und auswerten.</t>
+          <t>Du kannst Begründungen und Argumente formulieren.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr"/>
-      <c r="B72" s="2" t="inlineStr"/>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Sachunterricht</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Erkenntnisgewinnung</t>
+        </is>
+      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Du kannst (Stadtpläne, Baupläne, mehrschrittige Anleitungen, PC-Programme, Apps) lesen und nutzen.</t>
+          <t>Du kannst zielführend Fragen stellen, um Wissen zu erwerben und Sachthemen zu verstehen.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -1299,7 +1339,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Du wendest Problemlösestrategien (im Klassenrat, bei Interessenskonflikten, bei technischen Fragestellungen) an.</t>
+          <t>Du kannst zu Sachthemen recherchieren, indem du verschiedene Quellen (Sachtexte, Interviews, Bild-, Text- und Sachquellen) auswertest.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -1310,7 +1350,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Du kannst (Modelle, technische Konstruktionen) (planen, bauen, erklären) und dadurch Erkenntnisse über (Fahrzeuge, Türme, Brücken, Pflanzen, Körperteile) gewinnen.</t>
+          <t>Du kannst einen Versuch (zum Pflanzenwachstum, zum Sprudelgas, zur magnetischen Wirkung von Strom) planen, aufbauen, durchführen und auswerten.</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -1318,14 +1358,10 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr"/>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Kommunikation</t>
-        </is>
-      </c>
+      <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Du bringst dich in Unterrichtsgesprächen aktiv ein und zeigst dadurch dein Interesse an Sachthemen.</t>
+          <t>Du kannst Daten zu (untersuchten Bereich einfügen) erheben, darstellen und auswerten.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -1336,7 +1372,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Beobachtungen und Vermutungen von/ zu (Pflanzen, Tieren, Bildern, Gegenständen) äußern.</t>
+          <t>Du kannst (Stadtpläne, Baupläne, mehrschrittige Anleitungen, PC-Programme, Apps) lesen und nutzen.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -1347,7 +1383,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Du verwendest treffende Begriffe und sachlich angemessene Darstellungen (Symbole, Zeichnungen) zu den Sachthemen (Unterrichtsthemen einfügen).</t>
+          <t>Du wendest Problemlösestrategien (im Klassenrat, bei Interessenskonflikten, bei technischen Fragestellungen) an.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -1358,7 +1394,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Du nutzt geeignete Präsentations- und Darstellungsformen nach besprochenen Kriterien.</t>
+          <t>Du kannst (Modelle, technische Konstruktionen) (planen, bauen, erklären) und dadurch Erkenntnisse über (Fahrzeuge, Türme, Brücken, Pflanzen, Körperteile) gewinnen.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -1368,12 +1404,12 @@
       <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Bewertung</t>
+          <t>Kommunikation</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Du kannst mit anderen darüber diskutieren, ob Dargestelltes real oder fiktiv ist.</t>
+          <t>Du bringst dich in Unterrichtsgesprächen aktiv ein und zeigst dadurch dein Interesse an Sachthemen.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -1384,7 +1420,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Du kannst (Ereignisse, Gegenstände) in der Zeit einordnen.</t>
+          <t>Du kannst Beobachtungen und Vermutungen von/ zu (Pflanzen, Tieren, Bildern, Gegenständen) äußern.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
@@ -1395,7 +1431,7 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Du benennst Maßnahmen zur Erhaltung der eigenen Gesundheit (Zähne/ gesunde Ernährung/ mein Körper).</t>
+          <t>Du verwendest treffende Begriffe und sachlich angemessene Darstellungen (Symbole, Zeichnungen) zu den Sachthemen (Unterrichtsthemen einfügen).</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -1406,7 +1442,7 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Du kannst beschreiben, dass Umwelt und Natur im Sinne der Nachhaltigkeit geschützt werden müssen und gehst respektvoll mit Lebewesen um.</t>
+          <t>Du nutzt geeignete Präsentations- und Darstellungsformen nach besprochenen Kriterien.</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -1414,114 +1450,118 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr"/>
-      <c r="B83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Bewertung</t>
+        </is>
+      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Du kennst die Grundsätze des demokratischen Systems und wendest sie (im Klassenrat, bei Entscheidungsfindungen, politischen Diskussionen) an.</t>
+          <t>Du kannst mit anderen darüber diskutieren, ob Dargestelltes real oder fiktiv ist.</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Englisch</t>
-        </is>
-      </c>
+      <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>(Kompetenzen hier ergänzen)</t>
+          <t>Du kannst (Ereignisse, Gegenstände) in der Zeit einordnen.</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
+      <c r="A85" s="2" t="inlineStr"/>
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>(Kompetenzen hier ergänzen)</t>
+          <t>Du benennst Maßnahmen zur Erhaltung der eigenen Gesundheit (Zähne/ gesunde Ernährung/ mein Körper).</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Religion</t>
-        </is>
-      </c>
+      <c r="A86" s="2" t="inlineStr"/>
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>(Kompetenzen hier ergänzen)</t>
+          <t>Du kannst beschreiben, dass Umwelt und Natur im Sinne der Nachhaltigkeit geschützt werden müssen und gehst respektvoll mit Lebewesen um.</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Kunst</t>
-        </is>
-      </c>
+      <c r="A87" s="2" t="inlineStr"/>
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Du beteiligst dich an Unterrichtsgesprächen und zeigst so Interesse an künstlerischen Themen.</t>
+          <t>Du kennst die Grundsätze des demokratischen Systems und wendest sie (im Klassenrat, bei Entscheidungsfindungen, politischen Diskussionen) an.</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr"/>
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Du nutzt Buntstifte, Wasserfarben, Acrylfarben und selbst ausgewählte Bastelmaterialien für deine Werke.</t>
+          <t>(Kompetenzen hier ergänzen)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr"/>
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Du beachtest gestalterische Kriterien bei der Umsetzung eines Themas.</t>
+          <t>(Kompetenzen hier ergänzen)</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr"/>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Religion</t>
+        </is>
+      </c>
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Du hast eigene Ideen zur Gestaltung.</t>
+          <t>(Kompetenzen hier ergänzen)</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr"/>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Kunst</t>
+        </is>
+      </c>
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Du setzt deine Ideen selbstständig um.</t>
+          <t>Du beteiligst dich an Unterrichtsgesprächen und zeigst so Interesse an künstlerischen Themen.</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -1532,7 +1572,7 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Du stellst deine Werke in der vorgesehenen Zeit sinnvoll fertig.</t>
+          <t>Du nutzt Buntstifte, Wasserfarben, Acrylfarben und selbst ausgewählte Bastelmaterialien für deine Werke.</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -1543,7 +1583,7 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Tipps annehmen und sinnvoll für die eigene Arbeit nutzen.</t>
+          <t>Du beachtest gestalterische Kriterien bei der Umsetzung eines Themas.</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
@@ -1554,7 +1594,7 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Du kannst deine eigenen Kunstwerke und die anderer Künstler beschreiben.</t>
+          <t>Du hast eigene Ideen zur Gestaltung.</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
@@ -1565,7 +1605,7 @@
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Du begründest deine Meinung zu Kunstwerken.</t>
+          <t>Du setzt deine Ideen selbstständig um.</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
@@ -1576,7 +1616,7 @@
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Du kennst Fachbegriffe und nutzt sie passend.</t>
+          <t>Du stellst deine Werke in der vorgesehenen Zeit sinnvoll fertig.</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
@@ -1587,22 +1627,18 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Du kannst ausdrücken, ob du dich an die Gestaltungsvorgaben gehalten hast.</t>
+          <t>Du kannst Tipps annehmen und sinnvoll für die eigene Arbeit nutzen.</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Musik</t>
-        </is>
-      </c>
+      <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Du beteiligst dich interessiert an den musikalischen Aktivitäten.</t>
+          <t>Du kannst deine eigenen Kunstwerke und die anderer Künstler beschreiben.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
@@ -1613,7 +1649,7 @@
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Du beteiligst dich aktiv an Unterrichtsgesprächen.</t>
+          <t>Du begründest deine Meinung zu Kunstwerken.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
@@ -1624,7 +1660,7 @@
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Du findest passende Bewegungen und entwickelst Choreografien zu unterschiedlicher Musik.</t>
+          <t>Du kennst Fachbegriffe und nutzt sie passend.</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
@@ -1635,18 +1671,22 @@
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Rhythmen umsetzen.</t>
+          <t>Du kannst ausdrücken, ob du dich an die Gestaltungsvorgaben gehalten hast.</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr"/>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Musik</t>
+        </is>
+      </c>
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Du singst unsere Lieder mit.</t>
+          <t>Du beteiligst dich interessiert an den musikalischen Aktivitäten.</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
@@ -1657,7 +1697,7 @@
       <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Du tanzt vorgegebene Tänze nach.</t>
+          <t>Du beteiligst dich aktiv an Unterrichtsgesprächen.</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr"/>
@@ -1668,7 +1708,7 @@
       <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Du kennst alle Orff-Instrumente und spielst sie rhythmisch und technisch korrekt.</t>
+          <t>Du findest passende Bewegungen und entwickelst Choreografien zu unterschiedlicher Musik.</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
@@ -1679,7 +1719,7 @@
       <c r="B105" s="2" t="inlineStr"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Du kennst Orchester-Instrumente.</t>
+          <t>Du kannst Rhythmen umsetzen.</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
@@ -1690,7 +1730,7 @@
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Du kennst musikalische Gestaltungsmittel wie hoch-tief, laut-leise, schnell-langsam, traurig-fröhlich und kannst sie umsetzen.</t>
+          <t>Du singst unsere Lieder mit.</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
@@ -1701,7 +1741,7 @@
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Notenwerte benennen und umsetzen.</t>
+          <t>Du tanzt vorgegebene Tänze nach.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
@@ -1712,11 +1752,55 @@
       <c r="B108" s="2" t="inlineStr"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Du nutzt musikalische Fachbegriffe.</t>
+          <t>Du kennst alle Orff-Instrumente und spielst sie rhythmisch und technisch korrekt.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr"/>
+      <c r="B109" s="2" t="inlineStr"/>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Du kennst Orchester-Instrumente.</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr"/>
+      <c r="E109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr"/>
+      <c r="B110" s="2" t="inlineStr"/>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Du kennst musikalische Gestaltungsmittel wie hoch-tief, laut-leise, schnell-langsam, traurig-fröhlich und kannst sie umsetzen.</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr"/>
+      <c r="B111" s="2" t="inlineStr"/>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Du kannst Notenwerte benennen und umsetzen.</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr"/>
+      <c r="E111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr"/>
+      <c r="B112" s="2" t="inlineStr"/>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Du nutzt musikalische Fachbegriffe.</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/zeugnis-vorlage.xlsx
+++ b/zeugnis-vorlage.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +28,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,12 +53,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -424,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -583,11 +589,7 @@
           <t>Bewertung</t>
         </is>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Fachkommentar</t>
-        </is>
-      </c>
+      <c r="E9" s="1" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -606,7 +608,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr"/>
@@ -617,7 +619,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr"/>
@@ -628,7 +630,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr"/>
@@ -643,7 +645,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr"/>
@@ -654,7 +656,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr"/>
@@ -665,7 +667,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr"/>
@@ -676,7 +678,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr"/>
@@ -687,7 +689,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr"/>
@@ -698,7 +700,7 @@
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr"/>
@@ -709,7 +711,7 @@
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr"/>
@@ -724,7 +726,7 @@
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr"/>
@@ -735,7 +737,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr"/>
@@ -746,7 +748,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr"/>
@@ -757,7 +759,7 @@
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
-      <c r="E23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr"/>
@@ -768,7 +770,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr"/>
@@ -779,7 +781,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr"/>
@@ -790,7 +792,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr"/>
@@ -801,7 +803,7 @@
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr"/>
@@ -812,7 +814,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr"/>
@@ -823,7 +825,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr"/>
@@ -834,7 +836,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr"/>
@@ -845,7 +847,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr"/>
@@ -856,7 +858,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr"/>
@@ -867,7 +869,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
-      <c r="E33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr"/>
@@ -882,7 +884,7 @@
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr"/>
@@ -893,7 +895,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr"/>
@@ -904,7 +906,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr"/>
@@ -915,7 +917,7 @@
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
-      <c r="E37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr"/>
@@ -926,881 +928,969 @@
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr"/>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Kommentar</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Mathematik</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Zahl und Operation (Zahlenraum bis 1.000)</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Du kannst dich im Zahlenraum bis 1000 orientieren.</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Du kannst Additionsaufgaben (+) mit und ohne Übergänge lösen.</t>
-        </is>
-      </c>
       <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Additionsaufgaben halbschriftlich und schriftlich lösen.</t>
+          <t>Du kannst Additionsaufgaben (+) mit und ohne Übergänge lösen.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Subtraktionsaufgaben (-) mit und ohne Übergänge lösen.</t>
+          <t>Du kannst Additionsaufgaben halbschriftlich und schriftlich lösen.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Subtraktionsaufgaben mit Übertrag halbschriftlich und schriftlich lösen.</t>
+          <t>Du kannst Subtraktionsaufgaben (-) mit und ohne Übergänge lösen.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Du löst die Multiplikationsaufgaben (*) des kleinen Einmaleins automatisiert.</t>
+          <t>Du kannst Subtraktionsaufgaben mit Übertrag halbschriftlich und schriftlich lösen.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Du löst die Divisionsaufgaben (:) des kleinen Einmaleins automatisiert.</t>
+          <t>Du löst die Multiplikationsaufgaben (*) des kleinen Einmaleins automatisiert.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Divisionsaufgaben (:) mit Rest lösen.</t>
+          <t>Du löst die Divisionsaufgaben (:) des kleinen Einmaleins automatisiert.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Du wählst geeignete Rechenstrategien aus und wendest sie an.</t>
+          <t>Du kannst Divisionsaufgaben (:) mit Rest lösen.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Du nutzt geeignete Verfahren, um deine Ergebnisse zu überprüfen.</t>
+          <t>Du wählst geeignete Rechenstrategien aus und wendest sie an.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Sachaufgaben verstehen und eine passende Fragestellung entwickeln.</t>
+          <t>Du nutzt geeignete Verfahren, um deine Ergebnisse zu überprüfen.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Du kannst zu Sachaufgaben Lösungswege finden und eine passende Antwort formulieren.</t>
+          <t>Du kannst Sachaufgaben verstehen und eine passende Fragestellung entwickeln.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr"/>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Raum und Form</t>
-        </is>
-      </c>
+      <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Du kannst geometrischen Grundformen benennen und ihre besonderen Merkmale mit Fachbegriffen beschreiben.</t>
+          <t>Du kannst zu Sachaufgaben Lösungswege finden und eine passende Antwort formulieren.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
-      <c r="E51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr"/>
-      <c r="B52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Raum und Form</t>
+        </is>
+      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Du kannst geometrische Formen mit und ohne Lineal zeichnen.</t>
+          <t>Du kannst geometrischen Grundformen benennen und ihre besonderen Merkmale mit Fachbegriffen beschreiben.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Du vergrößerst oder verkleinerst Figuren nach Vorgaben.</t>
+          <t>Du kannst geometrische Formen mit und ohne Lineal zeichnen.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
-      <c r="E53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Du erkennst komplexere geometrische Muster und kannst diese fortsetzen.</t>
+          <t>Du vergrößerst oder verkleinerst Figuren nach Vorgaben.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Du kannst geometrische Körper benennen, mit Fachbegriffen beschreiben sie vergleichen und ihnen die entsprechenden Körpernetze zuordnen.</t>
+          <t>Du erkennst komplexere geometrische Muster und kannst diese fortsetzen.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Du überprüfst Figuren auf Achsensymmetrie und kannst zur Spiegelachse symmetrisch ergänzen.</t>
+          <t>Du kannst geometrische Körper benennen, mit Fachbegriffen beschreiben sie vergleichen und ihnen die entsprechenden Körpernetze zuordnen.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
-      <c r="E56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Lagebeziehungen und Ansichten beschreiben.</t>
+          <t>Du überprüfst Figuren auf Achsensymmetrie und kannst zur Spiegelachse symmetrisch ergänzen.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
-      <c r="E57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Lagepläne lesen und zeichnen sowie Wege auf Lageplänen finden, beschreiben und zeichnen.</t>
+          <t>Du kannst Lagebeziehungen und Ansichten beschreiben.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr"/>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Größen und Messen</t>
-        </is>
-      </c>
+      <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Uhrzeiten sekundengenau ablesen, einstellen und notieren.</t>
+          <t>Du kannst Lagepläne lesen und zeichnen sowie Wege auf Lageplänen finden, beschreiben und zeichnen.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
-      <c r="E59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr"/>
-      <c r="B60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Größen und Messen</t>
+        </is>
+      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Zeitspannen bestimmen.</t>
+          <t>Du kannst Uhrzeiten sekundengenau ablesen, einstellen und notieren.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
-      <c r="E60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Repräsentanten zu den Längeneinheiten mm, cm, m und km benennen und Längen abmessen.</t>
+          <t>Du kannst Zeitspannen bestimmen.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
-      <c r="E61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Längenangaben in unterschiedlichen Schreibweisen darstellen.</t>
+          <t>Du kannst Repräsentanten zu den Längeneinheiten mm, cm, m und km benennen und Längen abmessen.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Repräsentanten zu den Gewichtseinheiten g, kg und t benennen und Objekte wiegen.</t>
+          <t>Du kannst Längenangaben in unterschiedlichen Schreibweisen darstellen.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
-      <c r="E63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Gewichtsangaben in unterschiedlichen Schreibweisen darstellen.</t>
+          <t>Du kannst Repräsentanten zu den Gewichtseinheiten g, kg und t benennen und Objekte wiegen.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Geldbeträge mit Scheinen und Münzen darstellen, miteinander vergleichen und ordnen.</t>
+          <t>Du kannst Gewichtsangaben in unterschiedlichen Schreibweisen darstellen.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Du kannst mit Geldbeträgen rechnen.</t>
+          <t>Du kannst Geldbeträge mit Scheinen und Münzen darstellen, miteinander vergleichen und ordnen.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Daten und Zufall</t>
-        </is>
-      </c>
+      <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Daten aus einer Tabelle oder einem Diagramm ablesen bzw. selbst erheben und in eine andere Darstellungsform übertragen.</t>
+          <t>Du kannst mit Geldbeträgen rechnen.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
-      <c r="E67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr"/>
-      <c r="B68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Daten und Zufall</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Du kannst kombinatorische Aufgaben durch systematisches Vorgehen lösen und deine Lösung strategisch darstellen.</t>
+          <t>Du kannst Daten aus einer Tabelle oder einem Diagramm ablesen bzw. selbst erheben und in eine andere Darstellungsform übertragen.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Wahrscheinlichkeiten von einfachen Zufallsversuchen einschätzen, die Ergebnisse beschreiben und miteinander vergleichen.</t>
+          <t>Du kannst kombinatorische Aufgaben durch systematisches Vorgehen lösen und deine Lösung strategisch darstellen.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr"/>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Problemlösen, Modellieren, Argumentieren, Darstellen/Kommunizieren</t>
-        </is>
-      </c>
+      <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Du stellst deine Ideen verständlich dar und kannst deinen Lösungsweg erklären sowie mit anderen vergleichen.</t>
+          <t>Du kannst Wahrscheinlichkeiten von einfachen Zufallsversuchen einschätzen, die Ergebnisse beschreiben und miteinander vergleichen.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr"/>
-      <c r="B71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Problemlösen, Modellieren, Argumentieren, Darstellen/Kommunizieren</t>
+        </is>
+      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>Du stellst deine Ideen verständlich dar und kannst deinen Lösungsweg erklären sowie mit anderen vergleichen.</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
           <t>Du kannst Begründungen und Argumente formulieren.</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr"/>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Kommentar</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr"/>
+      <c r="D73" s="3" t="inlineStr"/>
+      <c r="E73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Sachunterricht</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Erkenntnisgewinnung</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Du kannst zielführend Fragen stellen, um Wissen zu erwerben und Sachthemen zu verstehen.</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr"/>
-      <c r="E72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr"/>
-      <c r="B73" s="2" t="inlineStr"/>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Du kannst zu Sachthemen recherchieren, indem du verschiedene Quellen (Sachtexte, Interviews, Bild-, Text- und Sachquellen) auswertest.</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
-      <c r="E73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr"/>
-      <c r="B74" s="2" t="inlineStr"/>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Du kannst einen Versuch (zum Pflanzenwachstum, zum Sprudelgas, zur magnetischen Wirkung von Strom) planen, aufbauen, durchführen und auswerten.</t>
-        </is>
-      </c>
       <c r="D74" s="2" t="inlineStr"/>
-      <c r="E74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Daten zu (untersuchten Bereich einfügen) erheben, darstellen und auswerten.</t>
+          <t>Du kannst zu Sachthemen recherchieren, indem du verschiedene Quellen (Sachtexte, Interviews, Bild-, Text- und Sachquellen) auswertest.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Du kannst (Stadtpläne, Baupläne, mehrschrittige Anleitungen, PC-Programme, Apps) lesen und nutzen.</t>
+          <t>Du kannst einen Versuch (zum Pflanzenwachstum, zum Sprudelgas, zur magnetischen Wirkung von Strom) planen, aufbauen, durchführen und auswerten.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
-      <c r="E76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Du wendest Problemlösestrategien (im Klassenrat, bei Interessenskonflikten, bei technischen Fragestellungen) an.</t>
+          <t>Du kannst Daten zu (untersuchten Bereich einfügen) erheben, darstellen und auswerten.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
-      <c r="E77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Du kannst (Modelle, technische Konstruktionen) (planen, bauen, erklären) und dadurch Erkenntnisse über (Fahrzeuge, Türme, Brücken, Pflanzen, Körperteile) gewinnen.</t>
+          <t>Du kannst (Stadtpläne, Baupläne, mehrschrittige Anleitungen, PC-Programme, Apps) lesen und nutzen.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
-      <c r="E78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr"/>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Kommunikation</t>
-        </is>
-      </c>
+      <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Du bringst dich in Unterrichtsgesprächen aktiv ein und zeigst dadurch dein Interesse an Sachthemen.</t>
+          <t>Du wendest Problemlösestrategien (im Klassenrat, bei Interessenskonflikten, bei technischen Fragestellungen) an.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
-      <c r="E79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Beobachtungen und Vermutungen von/ zu (Pflanzen, Tieren, Bildern, Gegenständen) äußern.</t>
+          <t>Du kannst (Modelle, technische Konstruktionen) (planen, bauen, erklären) und dadurch Erkenntnisse über (Fahrzeuge, Türme, Brücken, Pflanzen, Körperteile) gewinnen.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
-      <c r="E80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr"/>
-      <c r="B81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Kommunikation</t>
+        </is>
+      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Du verwendest treffende Begriffe und sachlich angemessene Darstellungen (Symbole, Zeichnungen) zu den Sachthemen (Unterrichtsthemen einfügen).</t>
+          <t>Du bringst dich in Unterrichtsgesprächen aktiv ein und zeigst dadurch dein Interesse an Sachthemen.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
-      <c r="E81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Du nutzt geeignete Präsentations- und Darstellungsformen nach besprochenen Kriterien.</t>
+          <t>Du kannst Beobachtungen und Vermutungen von/ zu (Pflanzen, Tieren, Bildern, Gegenständen) äußern.</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
-      <c r="E82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr"/>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Bewertung</t>
-        </is>
-      </c>
+      <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Du kannst mit anderen darüber diskutieren, ob Dargestelltes real oder fiktiv ist.</t>
+          <t>Du verwendest treffende Begriffe und sachlich angemessene Darstellungen (Symbole, Zeichnungen) zu den Sachthemen (Unterrichtsthemen einfügen).</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
-      <c r="E83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Du kannst (Ereignisse, Gegenstände) in der Zeit einordnen.</t>
+          <t>Du nutzt geeignete Präsentations- und Darstellungsformen nach besprochenen Kriterien.</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
-      <c r="E84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr"/>
-      <c r="B85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Bewertung</t>
+        </is>
+      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Du benennst Maßnahmen zur Erhaltung der eigenen Gesundheit (Zähne/ gesunde Ernährung/ mein Körper).</t>
+          <t>Du kannst mit anderen darüber diskutieren, ob Dargestelltes real oder fiktiv ist.</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
-      <c r="E85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr"/>
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Du kannst beschreiben, dass Umwelt und Natur im Sinne der Nachhaltigkeit geschützt werden müssen und gehst respektvoll mit Lebewesen um.</t>
+          <t>Du kannst (Ereignisse, Gegenstände) in der Zeit einordnen.</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
-      <c r="E86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr"/>
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Du kennst die Grundsätze des demokratischen Systems und wendest sie (im Klassenrat, bei Entscheidungsfindungen, politischen Diskussionen) an.</t>
+          <t>Du benennst Maßnahmen zur Erhaltung der eigenen Gesundheit (Zähne/ gesunde Ernährung/ mein Körper).</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
-      <c r="E87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Englisch</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="inlineStr"/>
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>(Kompetenzen hier ergänzen)</t>
+          <t>Du kannst beschreiben, dass Umwelt und Natur im Sinne der Nachhaltigkeit geschützt werden müssen und gehst respektvoll mit Lebewesen um.</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
-      <c r="E88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
+      <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>(Kompetenzen hier ergänzen)</t>
+          <t>Du kennst die Grundsätze des demokratischen Systems und wendest sie (im Klassenrat, bei Entscheidungsfindungen, politischen Diskussionen) an.</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
-      <c r="E89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Religion</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr"/>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>(Kompetenzen hier ergänzen)</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr"/>
-      <c r="E90" s="2" t="inlineStr"/>
+      <c r="A90" s="3" t="inlineStr"/>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Kommentar</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr"/>
+      <c r="D90" s="3" t="inlineStr"/>
+      <c r="E90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Kunst</t>
+          <t>Englisch</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Du beteiligst dich an Unterrichtsgesprächen und zeigst so Interesse an künstlerischen Themen.</t>
+          <t>(Kompetenzen hier ergänzen)</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
-      <c r="E91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr"/>
-      <c r="B92" s="2" t="inlineStr"/>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Du nutzt Buntstifte, Wasserfarben, Acrylfarben und selbst ausgewählte Bastelmaterialien für deine Werke.</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr"/>
-      <c r="E92" s="2" t="inlineStr"/>
+      <c r="A92" s="3" t="inlineStr"/>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Kommentar</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr"/>
+      <c r="D92" s="3" t="inlineStr"/>
+      <c r="E92" s="2" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr"/>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Du beachtest gestalterische Kriterien bei der Umsetzung eines Themas.</t>
+          <t>(Kompetenzen hier ergänzen)</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
-      <c r="E93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr"/>
-      <c r="B94" s="2" t="inlineStr"/>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Du hast eigene Ideen zur Gestaltung.</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr"/>
-      <c r="E94" s="2" t="inlineStr"/>
+      <c r="A94" s="3" t="inlineStr"/>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Kommentar</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr"/>
+      <c r="D94" s="3" t="inlineStr"/>
+      <c r="E94" s="2" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr"/>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Religion</t>
+        </is>
+      </c>
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Du setzt deine Ideen selbstständig um.</t>
+          <t>(Kompetenzen hier ergänzen)</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
-      <c r="E95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr"/>
-      <c r="B96" s="2" t="inlineStr"/>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Du stellst deine Werke in der vorgesehenen Zeit sinnvoll fertig.</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr"/>
-      <c r="E96" s="2" t="inlineStr"/>
+      <c r="A96" s="3" t="inlineStr"/>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Kommentar</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr"/>
+      <c r="D96" s="3" t="inlineStr"/>
+      <c r="E96" s="2" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr"/>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Kunst</t>
+        </is>
+      </c>
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Tipps annehmen und sinnvoll für die eigene Arbeit nutzen.</t>
+          <t>Du beteiligst dich an Unterrichtsgesprächen und zeigst so Interesse an künstlerischen Themen.</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
-      <c r="E97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Du kannst deine eigenen Kunstwerke und die anderer Künstler beschreiben.</t>
+          <t>Du nutzt Buntstifte, Wasserfarben, Acrylfarben und selbst ausgewählte Bastelmaterialien für deine Werke.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
-      <c r="E98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Du begründest deine Meinung zu Kunstwerken.</t>
+          <t>Du beachtest gestalterische Kriterien bei der Umsetzung eines Themas.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
-      <c r="E99" s="2" t="inlineStr"/>
+      <c r="E99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr"/>
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Du kennst Fachbegriffe und nutzt sie passend.</t>
+          <t>Du hast eigene Ideen zur Gestaltung.</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
-      <c r="E100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr"/>
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Du kannst ausdrücken, ob du dich an die Gestaltungsvorgaben gehalten hast.</t>
+          <t>Du setzt deine Ideen selbstständig um.</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
-      <c r="E101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Musik</t>
-        </is>
-      </c>
+      <c r="A102" s="2" t="inlineStr"/>
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Du beteiligst dich interessiert an den musikalischen Aktivitäten.</t>
+          <t>Du stellst deine Werke in der vorgesehenen Zeit sinnvoll fertig.</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
-      <c r="E102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr"/>
       <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Du beteiligst dich aktiv an Unterrichtsgesprächen.</t>
+          <t>Du kannst Tipps annehmen und sinnvoll für die eigene Arbeit nutzen.</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr"/>
-      <c r="E103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr"/>
       <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Du findest passende Bewegungen und entwickelst Choreografien zu unterschiedlicher Musik.</t>
+          <t>Du kannst deine eigenen Kunstwerke und die anderer Künstler beschreiben.</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
-      <c r="E104" s="2" t="inlineStr"/>
+      <c r="E104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr"/>
       <c r="B105" s="2" t="inlineStr"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Rhythmen umsetzen.</t>
+          <t>Du begründest deine Meinung zu Kunstwerken.</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
-      <c r="E105" s="2" t="inlineStr"/>
+      <c r="E105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr"/>
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Du singst unsere Lieder mit.</t>
+          <t>Du kennst Fachbegriffe und nutzt sie passend.</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
-      <c r="E106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr"/>
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Du tanzt vorgegebene Tänze nach.</t>
+          <t>Du kannst ausdrücken, ob du dich an die Gestaltungsvorgaben gehalten hast.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
-      <c r="E107" s="2" t="inlineStr"/>
+      <c r="E107" s="2" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr"/>
-      <c r="B108" s="2" t="inlineStr"/>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Du kennst alle Orff-Instrumente und spielst sie rhythmisch und technisch korrekt.</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr"/>
-      <c r="E108" s="2" t="inlineStr"/>
+      <c r="A108" s="3" t="inlineStr"/>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Kommentar</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr"/>
+      <c r="D108" s="3" t="inlineStr"/>
+      <c r="E108" s="2" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr"/>
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Musik</t>
+        </is>
+      </c>
       <c r="B109" s="2" t="inlineStr"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Du kennst Orchester-Instrumente.</t>
+          <t>Du beteiligst dich interessiert an den musikalischen Aktivitäten.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
-      <c r="E109" s="2" t="inlineStr"/>
+      <c r="E109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr"/>
       <c r="B110" s="2" t="inlineStr"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Du kennst musikalische Gestaltungsmittel wie hoch-tief, laut-leise, schnell-langsam, traurig-fröhlich und kannst sie umsetzen.</t>
+          <t>Du beteiligst dich aktiv an Unterrichtsgesprächen.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
-      <c r="E110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr"/>
       <c r="B111" s="2" t="inlineStr"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Du kannst Notenwerte benennen und umsetzen.</t>
+          <t>Du findest passende Bewegungen und entwickelst Choreografien zu unterschiedlicher Musik.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
-      <c r="E111" s="2" t="inlineStr"/>
+      <c r="E111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr"/>
       <c r="B112" s="2" t="inlineStr"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
+          <t>Du kannst Rhythmen umsetzen.</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr"/>
+      <c r="B113" s="2" t="inlineStr"/>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Du singst unsere Lieder mit.</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr"/>
+      <c r="E113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr"/>
+      <c r="B114" s="2" t="inlineStr"/>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Du tanzt vorgegebene Tänze nach.</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr"/>
+      <c r="E114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr"/>
+      <c r="B115" s="2" t="inlineStr"/>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Du kennst alle Orff-Instrumente und spielst sie rhythmisch und technisch korrekt.</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr"/>
+      <c r="E115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr"/>
+      <c r="B116" s="2" t="inlineStr"/>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Du kennst Orchester-Instrumente.</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr"/>
+      <c r="B117" s="2" t="inlineStr"/>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Du kennst musikalische Gestaltungsmittel wie hoch-tief, laut-leise, schnell-langsam, traurig-fröhlich und kannst sie umsetzen.</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr"/>
+      <c r="E117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr"/>
+      <c r="B118" s="2" t="inlineStr"/>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Du kannst Notenwerte benennen und umsetzen.</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr"/>
+      <c r="E118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr"/>
+      <c r="B119" s="2" t="inlineStr"/>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
           <t>Du nutzt musikalische Fachbegriffe.</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr"/>
-      <c r="E112" s="2" t="inlineStr"/>
+      <c r="D119" s="2" t="inlineStr"/>
+      <c r="E119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr"/>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>Kommentar</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr"/>
+      <c r="D120" s="3" t="inlineStr"/>
+      <c r="E120" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1822,17 +1912,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Bewertung</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Bedeutung</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
@@ -1931,7 +2021,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Hinweise</t>
         </is>
